--- a/data/trending_integrated_20261023_11.xlsx
+++ b/data/trending_integrated_20261023_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4360</v>
+        <v>4330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+16.27%</t>
+          <t>'+15.47%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="F2" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="G2" t="n">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>124263450398</v>
+        <v>126760957644</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -619,23 +619,23 @@
         <v>2500</v>
       </c>
       <c r="R2" t="n">
-        <v>-303000</v>
+        <v>-250000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>북한 도발 및 미국 시장 급등에 따른 방산주 상승세. 외인 매도 및 공매도 관련 언급.</t>
+          <t>북한 관련 지정학적 이슈와 연계된 방산주 강세. 외인 매도 및 공매도에 대한 비판.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['북한 도발', '방산주', '록히드마틴']</t>
+          <t>['방산주', '지정학', '공매도']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60200</v>
+        <v>60400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+8.66%</t>
+          <t>'+9.03%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F3" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G3" t="n">
-        <v>753</v>
+        <v>780</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>494525076850</v>
+        <v>503713143400</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -711,10 +711,10 @@
         <v>23150</v>
       </c>
       <c r="R3" t="n">
-        <v>824000</v>
+        <v>1319000</v>
       </c>
       <c r="S3" t="n">
-        <v>-7000</v>
+        <v>8000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8780</v>
+        <v>8730</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.15%</t>
+          <t>'+0.58%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H4" t="n">
         <v>5.11</v>
@@ -794,7 +794,7 @@
         <v>5.15</v>
       </c>
       <c r="O4" t="n">
-        <v>5756520220</v>
+        <v>5863497365</v>
       </c>
       <c r="P4" t="n">
         <v>15900</v>
@@ -803,7 +803,7 @@
         <v>6310</v>
       </c>
       <c r="R4" t="n">
-        <v>-186000</v>
+        <v>-311000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -839,162 +839,162 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13350</v>
+        <v>1218000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'-0.41%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>69</v>
+        <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>487</v>
       </c>
       <c r="G5" t="n">
-        <v>281</v>
+        <v>1342</v>
       </c>
       <c r="H5" t="n">
-        <v>2.92</v>
+        <v>48.77</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13340</v>
+        <v>1223000</v>
       </c>
       <c r="K5" t="n">
-        <v>12840</v>
+        <v>1200000</v>
       </c>
       <c r="L5" t="n">
-        <v>13700</v>
+        <v>1237000</v>
       </c>
       <c r="M5" t="n">
-        <v>12530</v>
+        <v>1171000</v>
       </c>
       <c r="N5" t="n">
-        <v>3.48</v>
+        <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>43937419980</v>
+        <v>2138639647000</v>
       </c>
       <c r="P5" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1640</v>
+        <v>468000</v>
       </c>
       <c r="R5" t="n">
-        <v>127000</v>
+        <v>-339000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>94000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>EUV 유리기판 기술력에 대한 기대감 및 외인 순매수 유입, 삼성 인수설 등 호재 기반 주가 상승 기대.</t>
+          <t>목표가 470만원 언급과 함께 주주 환원 발표 기대감. 정부의 시장 개입 및 연기금 손실에 대한 우려.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['EUV 유리기판', '기술력', '삼성 인수설']</t>
+          <t>['목표가', '주주환원', '연기금']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14430</v>
+        <v>13230</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.69%</t>
+          <t>'-0.82%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.06</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G6" t="n">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="H6" t="n">
-        <v>9.890000000000001</v>
+        <v>2.92</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14530</v>
+        <v>13340</v>
       </c>
       <c r="K6" t="n">
-        <v>14190</v>
+        <v>12840</v>
       </c>
       <c r="L6" t="n">
-        <v>14710</v>
+        <v>13700</v>
       </c>
       <c r="M6" t="n">
-        <v>13810</v>
+        <v>12530</v>
       </c>
       <c r="N6" t="n">
-        <v>9.949999999999999</v>
+        <v>3.48</v>
       </c>
       <c r="O6" t="n">
-        <v>18478432115</v>
+        <v>45527297340</v>
       </c>
       <c r="P6" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q6" t="n">
-        <v>3320</v>
+        <v>1640</v>
       </c>
       <c r="R6" t="n">
-        <v>-17000</v>
+        <v>-159000</v>
       </c>
       <c r="S6" t="n">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>실적 발표 이후 주가 하락세 지속, 공매도 및 주가 조작 의혹 제기, 대차 해지 동참 요구.</t>
+          <t>EUV 유리기판 기술력에 대한 기대감 및 외인 순매수 유입, 삼성 인수설 등 호재 기반 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적 발표', '공매도', '주가 조작']</t>
+          <t>['EUV 유리기판', '기술력', '삼성 인수설']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1213000</v>
+        <v>14370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.82%</t>
+          <t>'-1.10%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>61</v>
       </c>
       <c r="F7" t="n">
-        <v>489</v>
+        <v>30</v>
       </c>
       <c r="G7" t="n">
-        <v>1311</v>
+        <v>99</v>
       </c>
       <c r="H7" t="n">
-        <v>48.77</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1223000</v>
+        <v>14530</v>
       </c>
       <c r="K7" t="n">
-        <v>1200000</v>
+        <v>14190</v>
       </c>
       <c r="L7" t="n">
-        <v>1237000</v>
+        <v>14710</v>
       </c>
       <c r="M7" t="n">
-        <v>1171000</v>
+        <v>13810</v>
       </c>
       <c r="N7" t="n">
-        <v>48.79</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>2077535878500</v>
+        <v>19287643730</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>468000</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>-272000</v>
+        <v>-96000</v>
       </c>
       <c r="S7" t="n">
-        <v>79000</v>
+        <v>57000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정부 개입 및 연기금 손실 우려 속 주가 하락. 주주환원 발표 기대감 존재.</t>
+          <t>실적 발표 이후 주가 하락세 지속, 공매도 및 주가 조작 의혹 제기, 대차 해지 동참 요구.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['연기금', '주주환원', '정부 개입']</t>
+          <t>['실적 발표', '공매도', '주가 조작']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7120</v>
+        <v>7100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.52%</t>
+          <t>'-1.80%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G8" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H8" t="n">
         <v>25.42</v>
@@ -1162,7 +1162,7 @@
         <v>25.47</v>
       </c>
       <c r="O8" t="n">
-        <v>7664692345</v>
+        <v>8152215550</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1171,10 +1171,10 @@
         <v>7010</v>
       </c>
       <c r="R8" t="n">
-        <v>12000</v>
+        <v>-54000</v>
       </c>
       <c r="S8" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1207,70 +1207,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16810</v>
+        <v>207500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.11%</t>
+          <t>'-3.26%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.48</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>77</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>531</v>
       </c>
       <c r="G9" t="n">
-        <v>136</v>
+        <v>1313</v>
       </c>
       <c r="H9" t="n">
-        <v>3.77</v>
+        <v>46.13</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17350</v>
+        <v>214500</v>
       </c>
       <c r="K9" t="n">
-        <v>18130</v>
+        <v>206000</v>
       </c>
       <c r="L9" t="n">
-        <v>19070</v>
+        <v>212000</v>
       </c>
       <c r="M9" t="n">
-        <v>16530</v>
+        <v>203500</v>
       </c>
       <c r="N9" t="n">
-        <v>3.29</v>
+        <v>46.14</v>
       </c>
       <c r="O9" t="n">
-        <v>44722568845</v>
+        <v>1590306594750</v>
       </c>
       <c r="P9" t="n">
-        <v>22450</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>6320</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>-40000</v>
+        <v>-358000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>82000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 달리 국내 주가 부진, 주가 조작 의혹 및 수급 불안정으로 인한 하락 압력.</t>
+          <t>대통령 정치 성향 비판에 따른 개인적인 투자 손실 토로. 자사주 소각 및 지지율 하락 관련 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,90 +1279,90 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보안주', '주가 조작', '수급']</t>
+          <t>['정치', '자사주', '지지율']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>207250</v>
+        <v>16750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.38%</t>
+          <t>'-3.46%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>0.48</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>78</v>
       </c>
       <c r="F10" t="n">
-        <v>528</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>1343</v>
+        <v>137</v>
       </c>
       <c r="H10" t="n">
-        <v>46.13</v>
+        <v>3.77</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>214500</v>
+        <v>17350</v>
       </c>
       <c r="K10" t="n">
-        <v>206000</v>
+        <v>18130</v>
       </c>
       <c r="L10" t="n">
-        <v>212000</v>
+        <v>19070</v>
       </c>
       <c r="M10" t="n">
-        <v>203500</v>
+        <v>16530</v>
       </c>
       <c r="N10" t="n">
-        <v>46.14</v>
+        <v>3.29</v>
       </c>
       <c r="O10" t="n">
-        <v>1515920145500</v>
+        <v>45046291105</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>22450</v>
       </c>
       <c r="Q10" t="n">
-        <v>94500</v>
+        <v>6320</v>
       </c>
       <c r="R10" t="n">
-        <v>-319000</v>
+        <v>-11000</v>
       </c>
       <c r="S10" t="n">
-        <v>113000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 발언이 주를 이루며 주가 관련 정보 부재. 이재명 관련 부정적 언급 및 탄핵 주장.</t>
+          <t>미국 보안주 강세와 달리 국내 주가 부진, 주가 조작 의혹 및 수급 불안정으로 인한 하락 압력.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,20 +1371,20 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['보안주', '주가 조작', '수급']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16530</v>
+        <v>16560</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.56%</t>
+          <t>'-4.39%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F11" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G11" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="H11" t="n">
         <v>27.89</v>
@@ -1438,7 +1438,7 @@
         <v>27.87</v>
       </c>
       <c r="O11" t="n">
-        <v>16920064710</v>
+        <v>18262174290</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1447,10 +1447,10 @@
         <v>16450</v>
       </c>
       <c r="R11" t="n">
-        <v>-46000</v>
+        <v>16000</v>
       </c>
       <c r="S11" t="n">
-        <v>11000</v>
+        <v>19000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58700</v>
+        <v>58600</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.71%</t>
+          <t>'-4.87%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="F12" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G12" t="n">
-        <v>476</v>
+        <v>497</v>
       </c>
       <c r="H12" t="n">
         <v>22.25</v>
@@ -1530,7 +1530,7 @@
         <v>22.26</v>
       </c>
       <c r="O12" t="n">
-        <v>68352176800</v>
+        <v>70665093900</v>
       </c>
       <c r="P12" t="n">
         <v>139200</v>
@@ -1539,10 +1539,10 @@
         <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>-25000</v>
+        <v>-64000</v>
       </c>
       <c r="S12" t="n">
-        <v>-69000</v>
+        <v>-100000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9160</v>
+        <v>9190</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-9.22%</t>
+          <t>'-8.92%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.19</v>
       </c>
       <c r="E13" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="F13" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G13" t="n">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="H13" t="n">
         <v>2.5</v>
@@ -1616,13 +1616,13 @@
         <v>10060</v>
       </c>
       <c r="M13" t="n">
-        <v>9060</v>
+        <v>8940</v>
       </c>
       <c r="N13" t="n">
         <v>3.69</v>
       </c>
       <c r="O13" t="n">
-        <v>34260286030</v>
+        <v>36928089220</v>
       </c>
       <c r="P13" t="n">
         <v>11690</v>
@@ -1631,23 +1631,23 @@
         <v>2270</v>
       </c>
       <c r="R13" t="n">
-        <v>-5000</v>
+        <v>-33000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 급락 및 하한가 예상 의견 다수. 투자 경고 및 매도 의견 존재. 브릴스 수출 관련 뉴스 언급.</t>
+          <t>주가 급락 및 하한가 예상, 투자 주의 종목 지정 가능성 언급. 로봇 및 2차전지 테마 부재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['급락', '하한가', '브릴스']</t>
+          <t>['급락', '하한가', '테마']</t>
         </is>
       </c>
       <c r="X13" t="n">

--- a/data/trending_integrated_20261023_11.xlsx
+++ b/data/trending_integrated_20261023_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4330</v>
+        <v>4290</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+15.47%</t>
+          <t>'+14.40%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="F2" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="G2" t="n">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>126760957644</v>
+        <v>128174756699</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>북한 관련 지정학적 이슈와 연계된 방산주 강세. 외인 매도 및 공매도에 대한 비판.</t>
+          <t>북한 관련 지정학적 리스크와 연계된 방산주 상승에 대한 언급. 록히드마틴 급등, 코브라볼 포착 등 구체적인 뉴스 및 미국 시장 상황을 근거로 함.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['방산주', '지정학', '공매도']</t>
+          <t>['방산주', '지정학적 리스크', '록히드마틴']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60400</v>
+        <v>60100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+9.03%</t>
+          <t>'+8.48%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F3" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="G3" t="n">
-        <v>780</v>
+        <v>806</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>503713143400</v>
+        <v>511765507400</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8730</v>
+        <v>8710</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.58%</t>
+          <t>'+0.35%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F4" t="n">
         <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H4" t="n">
         <v>5.11</v>
@@ -794,7 +794,7 @@
         <v>5.15</v>
       </c>
       <c r="O4" t="n">
-        <v>5863497365</v>
+        <v>5940616815</v>
       </c>
       <c r="P4" t="n">
         <v>15900</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1218000</v>
+        <v>1217000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.41%</t>
+          <t>'-0.49%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="G5" t="n">
-        <v>1342</v>
+        <v>1352</v>
       </c>
       <c r="H5" t="n">
         <v>48.77</v>
@@ -886,7 +886,7 @@
         <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>2138639647000</v>
+        <v>2169863661500</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>목표가 470만원 언급과 함께 주주 환원 발표 기대감. 정부의 시장 개입 및 연기금 손실에 대한 우려.</t>
+          <t>목표가 상향, 주주환원 기대 등 긍정적 언급이 있으나, 정치적 발언과 연기금 관련 우려도 혼재됨. 구체적인 공시나 뉴스 기반 분석 부족.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13230</v>
+        <v>13200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.82%</t>
+          <t>'-1.05%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F6" t="n">
         <v>46</v>
       </c>
       <c r="G6" t="n">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="H6" t="n">
         <v>2.92</v>
@@ -978,7 +978,7 @@
         <v>3.48</v>
       </c>
       <c r="O6" t="n">
-        <v>45527297340</v>
+        <v>47370544010</v>
       </c>
       <c r="P6" t="n">
         <v>31500</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14370</v>
+        <v>14320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.10%</t>
+          <t>'-1.45%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G7" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="H7" t="n">
         <v>9.890000000000001</v>
@@ -1070,7 +1070,7 @@
         <v>9.949999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>19287643730</v>
+        <v>19631394280</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7100</v>
+        <v>7090</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.80%</t>
+          <t>'-1.94%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F8" t="n">
         <v>47</v>
       </c>
       <c r="G8" t="n">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="H8" t="n">
         <v>25.42</v>
@@ -1162,7 +1162,7 @@
         <v>25.47</v>
       </c>
       <c r="O8" t="n">
-        <v>8152215550</v>
+        <v>8290100265</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1207,70 +1207,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>207500</v>
+        <v>16790</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.26%</t>
+          <t>'-3.23%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>0.48</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>79</v>
       </c>
       <c r="F9" t="n">
-        <v>531</v>
+        <v>51</v>
       </c>
       <c r="G9" t="n">
-        <v>1313</v>
+        <v>137</v>
       </c>
       <c r="H9" t="n">
-        <v>46.13</v>
+        <v>3.77</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>214500</v>
+        <v>17350</v>
       </c>
       <c r="K9" t="n">
-        <v>206000</v>
+        <v>18130</v>
       </c>
       <c r="L9" t="n">
-        <v>212000</v>
+        <v>19070</v>
       </c>
       <c r="M9" t="n">
-        <v>203500</v>
+        <v>16530</v>
       </c>
       <c r="N9" t="n">
-        <v>46.14</v>
+        <v>3.29</v>
       </c>
       <c r="O9" t="n">
-        <v>1590306594750</v>
+        <v>45191728945</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>22450</v>
       </c>
       <c r="Q9" t="n">
-        <v>94500</v>
+        <v>6320</v>
       </c>
       <c r="R9" t="n">
-        <v>-358000</v>
+        <v>-11000</v>
       </c>
       <c r="S9" t="n">
-        <v>82000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>대통령 정치 성향 비판에 따른 개인적인 투자 손실 토로. 자사주 소각 및 지지율 하락 관련 언급.</t>
+          <t>미국 보안주 강세와 달리 국내 주가 부진, 주가 조작 의혹 및 수급 불안정으로 인한 하락 압력.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,90 +1279,90 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['정치', '자사주', '지지율']</t>
+          <t>['보안주', '주가 조작', '수급']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16750</v>
+        <v>207500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.46%</t>
+          <t>'-3.26%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.48</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>78</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>529</v>
       </c>
       <c r="G10" t="n">
-        <v>137</v>
+        <v>1285</v>
       </c>
       <c r="H10" t="n">
-        <v>3.77</v>
+        <v>46.13</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17350</v>
+        <v>214500</v>
       </c>
       <c r="K10" t="n">
-        <v>18130</v>
+        <v>206000</v>
       </c>
       <c r="L10" t="n">
-        <v>19070</v>
+        <v>212000</v>
       </c>
       <c r="M10" t="n">
-        <v>16530</v>
+        <v>203500</v>
       </c>
       <c r="N10" t="n">
-        <v>3.29</v>
+        <v>46.14</v>
       </c>
       <c r="O10" t="n">
-        <v>45046291105</v>
+        <v>1619435907000</v>
       </c>
       <c r="P10" t="n">
-        <v>22450</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>6320</v>
+        <v>94500</v>
       </c>
       <c r="R10" t="n">
-        <v>-11000</v>
+        <v>-358000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>82000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 달리 국내 주가 부진, 주가 조작 의혹 및 수급 불안정으로 인한 하락 압력.</t>
+          <t>이재명 정치 관련 언급이 압도적이며, 주가 관련 내용은 '양전', '플러스', '바닥', '자사주소각' 등으로 매우 단편적임. 실질적 근거 없는 정치적 논쟁이 주를 이룸.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,20 +1371,20 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['보안주', '주가 조작', '수급']</t>
+          <t>['정치', '이재명', '주가']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16560</v>
+        <v>16510</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.39%</t>
+          <t>'-4.68%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F11" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="H11" t="n">
         <v>27.89</v>
@@ -1438,7 +1438,7 @@
         <v>27.87</v>
       </c>
       <c r="O11" t="n">
-        <v>18262174290</v>
+        <v>18704005740</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58600</v>
+        <v>58400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.87%</t>
+          <t>'-5.19%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F12" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G12" t="n">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="H12" t="n">
         <v>22.25</v>
@@ -1530,7 +1530,7 @@
         <v>22.26</v>
       </c>
       <c r="O12" t="n">
-        <v>70665093900</v>
+        <v>72461433900</v>
       </c>
       <c r="P12" t="n">
         <v>139200</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9190</v>
+        <v>9110</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-8.92%</t>
+          <t>'-9.71%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.19</v>
       </c>
       <c r="E13" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F13" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G13" t="n">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="H13" t="n">
         <v>2.5</v>
@@ -1622,7 +1622,7 @@
         <v>3.69</v>
       </c>
       <c r="O13" t="n">
-        <v>36928089220</v>
+        <v>37460074070</v>
       </c>
       <c r="P13" t="n">
         <v>11690</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 급락 및 하한가 예상, 투자 주의 종목 지정 가능성 언급. 로봇 및 2차전지 테마 부재.</t>
+          <t>급락 및 하한가 가능성 언급이 지배적. '투자주의' 해제 기대감도 있으나, 전반적으로 부정적인 차트 분석과 하락 전망이 주를 이룸. 브릴스 관련 뉴스가 있으나 종목 자체에 대한 직접적 영향은 불명확.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['급락', '하한가', '테마']</t>
+          <t>['급락', '하한가', '투자주의']</t>
         </is>
       </c>
       <c r="X13" t="n">

--- a/data/trending_integrated_20261023_11.xlsx
+++ b/data/trending_integrated_20261023_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4290</v>
+        <v>4210</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+14.40%</t>
+          <t>'+12.27%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="F2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G2" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>128174756699</v>
+        <v>131200595346</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>북한 관련 지정학적 리스크와 연계된 방산주 상승에 대한 언급. 록히드마틴 급등, 코브라볼 포착 등 구체적인 뉴스 및 미국 시장 상황을 근거로 함.</t>
+          <t>북한 관련 지정학적 리스크 부각 및 방산주 상승 기대감. 외인 매도 및 주가 조작 의혹 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['방산주', '지정학적 리스크', '록히드마틴']</t>
+          <t>['지정학적 리스크', '방산주', '외인 매도']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60100</v>
+        <v>60500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+8.48%</t>
+          <t>'+9.21%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F3" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G3" t="n">
-        <v>806</v>
+        <v>832</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>511765507400</v>
+        <v>520024338950</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외인·기관의 삼성E&amp;A 대규모 매수세 유입, MSCI 패시브 자금 유입 및 자사주 매입·소각 공시 기반 주가 상승 전망.</t>
+          <t>외국인 및 기관 순매수와 자사주 매입/소각 공시 기반 주가 방어 및 상승 전망. MSCI 편입 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>[' MSCI', '자사주 매입', '패시브 자금']</t>
+          <t>['자사주 매입', 'MSCI 편입', '수급']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G4" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H4" t="n">
         <v>5.11</v>
@@ -794,7 +794,7 @@
         <v>5.15</v>
       </c>
       <c r="O4" t="n">
-        <v>5940616815</v>
+        <v>6000906785</v>
       </c>
       <c r="P4" t="n">
         <v>15900</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>신약 개발 및 임상 성공 기대감 대비 부진한 주가 흐름. 주가 조작 및 허풍 관련 의혹 제기.</t>
+          <t>해외 특허에도 불구하고 주가 부양 미흡, 일부 투자자들의 비판과 함께 단타 매매 언급. 허풍제약이라는 부정적 별칭 등장.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['신약 개발', '임상', '주가 조작']</t>
+          <t>['뇌졸증 치료제', '단주거래', '신약개발']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1217000</v>
+        <v>1222000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.49%</t>
+          <t>'-0.08%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G5" t="n">
-        <v>1352</v>
+        <v>1255</v>
       </c>
       <c r="H5" t="n">
         <v>48.77</v>
@@ -886,7 +886,7 @@
         <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>2169863661500</v>
+        <v>2212336983000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>목표가 상향, 주주환원 기대 등 긍정적 언급이 있으나, 정치적 발언과 연기금 관련 우려도 혼재됨. 구체적인 공시나 뉴스 기반 분석 부족.</t>
+          <t>정부 정책 및 연기금의 매도에 대한 부정적 전망. 주주환원 발표 기대감과 솔리다임 상장 중단 이슈.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['목표가', '주주환원', '연기금']</t>
+          <t>['연기금 매도', '주주환원', '솔리다임']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13200</v>
+        <v>13300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.05%</t>
+          <t>'-0.30%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6" t="n">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="H6" t="n">
         <v>2.92</v>
@@ -978,7 +978,7 @@
         <v>3.48</v>
       </c>
       <c r="O6" t="n">
-        <v>47370544010</v>
+        <v>48652857935</v>
       </c>
       <c r="P6" t="n">
         <v>31500</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>EUV 유리기판 기술력에 대한 기대감 및 외인 순매수 유입, 삼성 인수설 등 호재 기반 주가 상승 기대.</t>
+          <t>EUV 유리기판 기술력에 대한 긍정적 전망 및 삼성 인수설. 미장 통신주 하락에도 불구하고 개인 투자자 지지.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14320</v>
+        <v>14410</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.45%</t>
+          <t>'-0.83%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F7" t="n">
         <v>31</v>
       </c>
       <c r="G7" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="H7" t="n">
         <v>9.890000000000001</v>
@@ -1070,7 +1070,7 @@
         <v>9.949999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>19631394280</v>
+        <v>20492352215</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7090</v>
+        <v>7080</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.94%</t>
+          <t>'-2.07%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="H8" t="n">
         <v>25.42</v>
@@ -1162,7 +1162,7 @@
         <v>25.47</v>
       </c>
       <c r="O8" t="n">
-        <v>8290100265</v>
+        <v>8634471665</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>컨센서스 상회하는 호실적 발표 및 재무 상태 개선, 신사업 모멘텀 및 배당 기대감으로 인한 주가 반등 전망.</t>
+          <t>양호한 순이익 발표에도 목표가 하향 및 공매도 관련 부정적 언급. 외인/기관 순매수와 저가 매수 기회 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['호실적', '신사업', '배당']</t>
+          <t>['순이익', '공매도', '외인 순매수']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16790</v>
+        <v>16900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.23%</t>
+          <t>'-2.59%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.48</v>
       </c>
       <c r="E9" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G9" t="n">
         <v>137</v>
@@ -1254,7 +1254,7 @@
         <v>3.29</v>
       </c>
       <c r="O9" t="n">
-        <v>45191728945</v>
+        <v>45423761005</v>
       </c>
       <c r="P9" t="n">
         <v>22450</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 달리 국내 주가 부진, 주가 조작 의혹 및 수급 불안정으로 인한 하락 압력.</t>
+          <t>미국 증시 하락 및 보안주 상승 속에서 종목 자체의 부정적 전망. 주가 조작, 무빙 최악, 수급 부족 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보안주', '주가 조작', '수급']</t>
+          <t>['미국 증시', '보안주', '수급']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>207500</v>
+        <v>208250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.26%</t>
+          <t>'-2.91%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="G10" t="n">
-        <v>1285</v>
+        <v>1350</v>
       </c>
       <c r="H10" t="n">
         <v>46.13</v>
@@ -1346,7 +1346,7 @@
         <v>46.14</v>
       </c>
       <c r="O10" t="n">
-        <v>1619435907000</v>
+        <v>1659543486500</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>이재명 정치 관련 언급이 압도적이며, 주가 관련 내용은 '양전', '플러스', '바닥', '자사주소각' 등으로 매우 단편적임. 실질적 근거 없는 정치적 논쟁이 주를 이룸.</t>
+          <t>정치적 이슈로 인한 부정적 전망 및 연기금 매도 언급. 주가 바닥론과 자사주 소각 기대감 혼재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['정치', '이재명', '주가']</t>
+          <t>['정치적 이슈', '연기금 매도', '자사주 소각']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16510</v>
+        <v>16530</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.68%</t>
+          <t>'-4.56%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H11" t="n">
         <v>27.89</v>
@@ -1438,7 +1438,7 @@
         <v>27.87</v>
       </c>
       <c r="O11" t="n">
-        <v>18704005740</v>
+        <v>19424533270</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>조선업종 전반의 하락세 속 주가 부진 지속, 주주환원 정책 및 공매도 금지 요구.</t>
+          <t>정치적 이슈와 조선업 부진에 따른 부정적 전망. 주주환원 정책 및 공매도 금지 요청.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['조선업', '주주환원', '공매도']</t>
+          <t>['정치적 이슈', '조선업', '주주환원']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58400</v>
+        <v>58500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.19%</t>
+          <t>'-5.03%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="F12" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G12" t="n">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="H12" t="n">
         <v>22.25</v>
@@ -1530,7 +1530,7 @@
         <v>22.26</v>
       </c>
       <c r="O12" t="n">
-        <v>72461433900</v>
+        <v>75250610750</v>
       </c>
       <c r="P12" t="n">
         <v>139200</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미 증시 폭락 영향 및 공매도 물량 부담으로 인한 주가 하락세 지속, 정부 정책 및 무능 비판.</t>
+          <t>증시 하락 및 공매도 물량 증가에 따른 부정적 전망. 정부 정책 및 개인 투자자 경험 기반 분석.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['미 증시', '공매도', '주가 하락']</t>
+          <t>['공매도', '증시 하락', '정부 정책']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9110</v>
+        <v>9060</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-9.71%</t>
+          <t>'-10.21%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.19</v>
       </c>
       <c r="E13" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F13" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G13" t="n">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="H13" t="n">
         <v>2.5</v>
@@ -1622,7 +1622,7 @@
         <v>3.69</v>
       </c>
       <c r="O13" t="n">
-        <v>37460074070</v>
+        <v>38498103340</v>
       </c>
       <c r="P13" t="n">
         <v>11690</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>급락 및 하한가 가능성 언급이 지배적. '투자주의' 해제 기대감도 있으나, 전반적으로 부정적인 차트 분석과 하락 전망이 주를 이룸. 브릴스 관련 뉴스가 있으나 종목 자체에 대한 직접적 영향은 불명확.</t>
+          <t>주가 급락 및 조정, 횡보 예상. 투자주의 해지 가능성 및 수급 부진 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['급락', '하한가', '투자주의']</t>
+          <t>['주가 급락', '조정', '수급']</t>
         </is>
       </c>
       <c r="X13" t="n">

--- a/data/trending_integrated_20261023_11.xlsx
+++ b/data/trending_integrated_20261023_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4210</v>
+        <v>4225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+12.27%</t>
+          <t>'+12.67%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="F2" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="G2" t="n">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>131200595346</v>
+        <v>132443434725</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>북한 관련 지정학적 리스크 부각 및 방산주 상승 기대감. 외인 매도 및 주가 조작 의혹 언급.</t>
+          <t>북한 도발 관련 방산주 록히드마틴 급등, 코브라볼 포착 등 지정학적 리스크 부각.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['지정학적 리스크', '방산주', '외인 매도']</t>
+          <t>['북한 도발', '방산주', '코브라볼']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="F3" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G3" t="n">
-        <v>832</v>
+        <v>841</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>520024338950</v>
+        <v>526295690250</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외국인 및 기관 순매수와 자사주 매입/소각 공시 기반 주가 방어 및 상승 전망. MSCI 편입 가능성 언급.</t>
+          <t>외인·기관의 대규모 자사주 매입 및 매각 자금 유입, MSCI 패시브 자금 유입 전망에 따른 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['자사주 매입', 'MSCI 편입', '수급']</t>
+          <t>['자사주 매입', 'MSCI 패시브']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8710</v>
+        <v>13450</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.35%</t>
+          <t>'+0.82%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.04</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G4" t="n">
-        <v>176</v>
+        <v>340</v>
       </c>
       <c r="H4" t="n">
-        <v>5.11</v>
+        <v>2.92</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8680</v>
+        <v>13340</v>
       </c>
       <c r="K4" t="n">
-        <v>9410</v>
+        <v>12840</v>
       </c>
       <c r="L4" t="n">
-        <v>9460</v>
+        <v>13700</v>
       </c>
       <c r="M4" t="n">
-        <v>8640</v>
+        <v>12530</v>
       </c>
       <c r="N4" t="n">
-        <v>5.15</v>
+        <v>3.48</v>
       </c>
       <c r="O4" t="n">
-        <v>6000906785</v>
+        <v>49905330235</v>
       </c>
       <c r="P4" t="n">
-        <v>15900</v>
+        <v>31500</v>
       </c>
       <c r="Q4" t="n">
-        <v>6310</v>
+        <v>1640</v>
       </c>
       <c r="R4" t="n">
-        <v>-311000</v>
+        <v>-159000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>해외 특허에도 불구하고 주가 부양 미흡, 일부 투자자들의 비판과 함께 단타 매매 언급. 허풍제약이라는 부정적 별칭 등장.</t>
+          <t>EUV 유리기판 관련 기술성 부각, 삼성 인수설 및 외인 매수세 유입, SK하이닉스 반등에 따른 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['뇌졸증 치료제', '단주거래', '신약개발']</t>
+          <t>['유리기판', 'EUV', '외인 매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1222000</v>
+        <v>1228000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.08%</t>
+          <t>'+0.41%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G5" t="n">
-        <v>1255</v>
+        <v>1233</v>
       </c>
       <c r="H5" t="n">
         <v>48.77</v>
@@ -886,7 +886,7 @@
         <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>2212336983000</v>
+        <v>2261369728000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정부 정책 및 연기금의 매도에 대한 부정적 전망. 주주환원 발표 기대감과 솔리다임 상장 중단 이슈.</t>
+          <t>정부 개입 및 연기금 손실 우려 속 주주환원 발표 기대감, 솔리다임 IPO 중단 소식.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['연기금 매도', '주주환원', '솔리다임']</t>
+          <t>['정부 개입', '주주환원', '솔리다임']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13300</v>
+        <v>8700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.30%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="F6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G6" t="n">
-        <v>325</v>
+        <v>176</v>
       </c>
       <c r="H6" t="n">
-        <v>2.92</v>
+        <v>5.11</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13340</v>
+        <v>8680</v>
       </c>
       <c r="K6" t="n">
-        <v>12840</v>
+        <v>9410</v>
       </c>
       <c r="L6" t="n">
-        <v>13700</v>
+        <v>9460</v>
       </c>
       <c r="M6" t="n">
-        <v>12530</v>
+        <v>8640</v>
       </c>
       <c r="N6" t="n">
-        <v>3.48</v>
+        <v>5.15</v>
       </c>
       <c r="O6" t="n">
-        <v>48652857935</v>
+        <v>6068871400</v>
       </c>
       <c r="P6" t="n">
-        <v>31500</v>
+        <v>15900</v>
       </c>
       <c r="Q6" t="n">
-        <v>1640</v>
+        <v>6310</v>
       </c>
       <c r="R6" t="n">
-        <v>-159000</v>
+        <v>-311000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>EUV 유리기판 기술력에 대한 긍정적 전망 및 삼성 인수설. 미장 통신주 하락에도 불구하고 개인 투자자 지지.</t>
+          <t>해외 특허에도 불구하고 주가 부양 미흡, 일부 투자자들의 비판과 함께 단타 매매 언급. 허풍제약이라는 부정적 별칭 등장.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['EUV 유리기판', '기술력', '삼성 인수설']</t>
+          <t>['뇌졸증 치료제', '단주거래', '신약개발']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14410</v>
+        <v>14470</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.83%</t>
+          <t>'-0.41%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F7" t="n">
         <v>31</v>
       </c>
       <c r="G7" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H7" t="n">
         <v>9.890000000000001</v>
@@ -1070,7 +1070,7 @@
         <v>9.949999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>20492352215</v>
+        <v>21074291855</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7080</v>
+        <v>17100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.07%</t>
+          <t>'-1.44%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>0.48</v>
       </c>
       <c r="E8" t="n">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="F8" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G8" t="n">
-        <v>307</v>
+        <v>137</v>
       </c>
       <c r="H8" t="n">
-        <v>25.42</v>
+        <v>3.77</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7230</v>
+        <v>17350</v>
       </c>
       <c r="K8" t="n">
-        <v>7100</v>
+        <v>18130</v>
       </c>
       <c r="L8" t="n">
-        <v>7220</v>
+        <v>19070</v>
       </c>
       <c r="M8" t="n">
-        <v>7010</v>
+        <v>16530</v>
       </c>
       <c r="N8" t="n">
-        <v>25.47</v>
+        <v>3.29</v>
       </c>
       <c r="O8" t="n">
-        <v>8634471665</v>
+        <v>45785819880</v>
       </c>
       <c r="P8" t="n">
-        <v>17950</v>
+        <v>22450</v>
       </c>
       <c r="Q8" t="n">
-        <v>7010</v>
+        <v>6320</v>
       </c>
       <c r="R8" t="n">
-        <v>-54000</v>
+        <v>-11000</v>
       </c>
       <c r="S8" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>양호한 순이익 발표에도 목표가 하향 및 공매도 관련 부정적 언급. 외인/기관 순매수와 저가 매수 기회 언급.</t>
+          <t>미국 증시 하락 및 보안주 상승 속에서 종목 자체의 부정적 전망. 주가 조작, 무빙 최악, 수급 부족 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['순이익', '공매도', '외인 순매수']</t>
+          <t>['미국 증시', '보안주', '수급']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16900</v>
+        <v>7080</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.59%</t>
+          <t>'-2.07%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.48</v>
+        <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="F9" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>137</v>
+        <v>320</v>
       </c>
       <c r="H9" t="n">
-        <v>3.77</v>
+        <v>25.42</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17350</v>
+        <v>7230</v>
       </c>
       <c r="K9" t="n">
-        <v>18130</v>
+        <v>7100</v>
       </c>
       <c r="L9" t="n">
-        <v>19070</v>
+        <v>7220</v>
       </c>
       <c r="M9" t="n">
-        <v>16530</v>
+        <v>7010</v>
       </c>
       <c r="N9" t="n">
-        <v>3.29</v>
+        <v>25.47</v>
       </c>
       <c r="O9" t="n">
-        <v>45423761005</v>
+        <v>9057747745</v>
       </c>
       <c r="P9" t="n">
-        <v>22450</v>
+        <v>17950</v>
       </c>
       <c r="Q9" t="n">
-        <v>6320</v>
+        <v>7010</v>
       </c>
       <c r="R9" t="n">
-        <v>-11000</v>
+        <v>-54000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 증시 하락 및 보안주 상승 속에서 종목 자체의 부정적 전망. 주가 조작, 무빙 최악, 수급 부족 언급.</t>
+          <t>분기 순이익 컨센서스 상회에도 목표가 하향, FLiPP 신사업 및 재무 개선 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['미국 증시', '보안주', '수급']</t>
+          <t>['순이익', 'FLiPP', '재무 개선']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>208250</v>
+        <v>209500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.91%</t>
+          <t>'-2.33%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>527</v>
       </c>
       <c r="G10" t="n">
-        <v>1350</v>
+        <v>1397</v>
       </c>
       <c r="H10" t="n">
         <v>46.13</v>
@@ -1346,7 +1346,7 @@
         <v>46.14</v>
       </c>
       <c r="O10" t="n">
-        <v>1659543486500</v>
+        <v>1697534455250</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 이슈로 인한 부정적 전망 및 연기금 매도 언급. 주가 바닥론과 자사주 소각 기대감 혼재.</t>
+          <t>현 정부 정책에 대한 비판과 연기금 매도, 자사주 소각 기대감 혼재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '연기금 매도', '자사주 소각']</t>
+          <t>['정부 정책', '연기금']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16530</v>
+        <v>16560</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.56%</t>
+          <t>'-4.39%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F11" t="n">
         <v>56</v>
       </c>
       <c r="G11" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="H11" t="n">
         <v>27.89</v>
@@ -1438,7 +1438,7 @@
         <v>27.87</v>
       </c>
       <c r="O11" t="n">
-        <v>19424533270</v>
+        <v>19925105995</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈와 조선업 부진에 따른 부정적 전망. 주주환원 정책 및 공매도 금지 요청.</t>
+          <t>주가 하락세 속 주주환원 정책 발표 가능성 및 코스피 4천 목표치 제시, 조선업 부진.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '조선업', '주주환원']</t>
+          <t>['주주환원', '조선업']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58500</v>
+        <v>58600</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.03%</t>
+          <t>'-4.87%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G12" t="n">
-        <v>520</v>
+        <v>535</v>
       </c>
       <c r="H12" t="n">
         <v>22.25</v>
@@ -1530,7 +1530,7 @@
         <v>22.26</v>
       </c>
       <c r="O12" t="n">
-        <v>75250610750</v>
+        <v>78174897550</v>
       </c>
       <c r="P12" t="n">
         <v>139200</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9060</v>
+        <v>9100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-10.21%</t>
+          <t>'-9.81%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.19</v>
       </c>
       <c r="E13" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F13" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G13" t="n">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="H13" t="n">
         <v>2.5</v>
@@ -1622,7 +1622,7 @@
         <v>3.69</v>
       </c>
       <c r="O13" t="n">
-        <v>38498103340</v>
+        <v>39401961375</v>
       </c>
       <c r="P13" t="n">
         <v>11690</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 급락 및 조정, 횡보 예상. 투자주의 해지 가능성 및 수급 부진 언급.</t>
+          <t>조정 및 횡보 예상, 하한가 및 급락 가능성 언급, 신사업 및 투자 주의 해제 기대감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가 급락', '조정', '수급']</t>
+          <t>['조정', '하한가', '신사업']</t>
         </is>
       </c>
       <c r="X13" t="n">

--- a/data/trending_integrated_20261023_11.xlsx
+++ b/data/trending_integrated_20261023_11.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F2" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G2" t="n">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>132443434725</v>
+        <v>133015249139</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>북한 도발 관련 방산주 록히드마틴 급등, 코브라볼 포착 등 지정학적 리스크 부각.</t>
+          <t>북한 관련 지정학적 이슈 부각, 방산주(록히드마틴) 급등에 따른 기대감 반영.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['북한 도발', '방산주', '코브라볼']</t>
+          <t>['지정학적 이슈', '방산주', '록히드마틴']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60500</v>
+        <v>60800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+9.21%</t>
+          <t>'+9.75%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="F3" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G3" t="n">
-        <v>841</v>
+        <v>861</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>526295690250</v>
+        <v>531933367200</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13450</v>
+        <v>13400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.82%</t>
+          <t>'+0.45%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="H4" t="n">
         <v>2.92</v>
@@ -794,7 +794,7 @@
         <v>3.48</v>
       </c>
       <c r="O4" t="n">
-        <v>49905330235</v>
+        <v>50810300480</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="G5" t="n">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="H5" t="n">
         <v>48.77</v>
@@ -886,7 +886,7 @@
         <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>2261369728000</v>
+        <v>2301400015000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정부 개입 및 연기금 손실 우려 속 주주환원 발표 기대감, 솔리다임 IPO 중단 소식.</t>
+          <t>솔리다임 IPO 중단, 실적 발표 및 주주환원 기대감 공존. 외인/기관 매도세 확인.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['정부 개입', '주주환원', '솔리다임']</t>
+          <t>['IPO', '실적 발표', '주주환원']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8700</v>
+        <v>8690</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -978,7 +978,7 @@
         <v>5.15</v>
       </c>
       <c r="O6" t="n">
-        <v>6068871400</v>
+        <v>6118694940</v>
       </c>
       <c r="P6" t="n">
         <v>15900</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14470</v>
+        <v>14460</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.41%</t>
+          <t>'-0.48%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G7" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H7" t="n">
         <v>9.890000000000001</v>
@@ -1070,7 +1070,7 @@
         <v>9.949999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>21074291855</v>
+        <v>21406104885</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17100</v>
+        <v>17090</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.44%</t>
+          <t>'-1.50%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.48</v>
       </c>
       <c r="E8" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F8" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G8" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H8" t="n">
         <v>3.77</v>
@@ -1162,7 +1162,7 @@
         <v>3.29</v>
       </c>
       <c r="O8" t="n">
-        <v>45785819880</v>
+        <v>45928558135</v>
       </c>
       <c r="P8" t="n">
         <v>22450</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7080</v>
+        <v>7070</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.07%</t>
+          <t>'-2.21%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F9" t="n">
         <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="H9" t="n">
         <v>25.42</v>
@@ -1254,7 +1254,7 @@
         <v>25.47</v>
       </c>
       <c r="O9" t="n">
-        <v>9057747745</v>
+        <v>9308188940</v>
       </c>
       <c r="P9" t="n">
         <v>17950</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>분기 순이익 컨센서스 상회에도 목표가 하향, FLiPP 신사업 및 재무 개선 기대감.</t>
+          <t>긍정적 순이익 수치 언급, 목표가 하향 추세 속 외인/기관 순매수 동향.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['순이익', 'FLiPP', '재무 개선']</t>
+          <t>['순이익', '목표가', '외인/기관']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G10" t="n">
-        <v>1397</v>
+        <v>1503</v>
       </c>
       <c r="H10" t="n">
         <v>46.13</v>
@@ -1346,7 +1346,7 @@
         <v>46.14</v>
       </c>
       <c r="O10" t="n">
-        <v>1697534455250</v>
+        <v>1729189966000</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>현 정부 정책에 대한 비판과 연기금 매도, 자사주 소각 기대감 혼재.</t>
+          <t>정치 관련 부정적 언급 다수, 연기금 매도세 및 자사주 소각 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['정부 정책', '연기금']</t>
+          <t>['정치', '연기금', '자사주']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16560</v>
+        <v>16550</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.39%</t>
+          <t>'-4.45%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F11" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G11" t="n">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="H11" t="n">
         <v>27.89</v>
@@ -1438,7 +1438,7 @@
         <v>27.87</v>
       </c>
       <c r="O11" t="n">
-        <v>19925105995</v>
+        <v>20269907845</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주가 하락세 속 주주환원 정책 발표 가능성 및 코스피 4천 목표치 제시, 조선업 부진.</t>
+          <t>주가 하락 및 정치 관련 부정적 언급, 조선주 전반의 약세 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주주환원', '조선업']</t>
+          <t>['주가 하락', '정치', '조선주']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58600</v>
+        <v>58500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.87%</t>
+          <t>'-5.03%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F12" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G12" t="n">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="H12" t="n">
         <v>22.25</v>
@@ -1530,7 +1530,7 @@
         <v>22.26</v>
       </c>
       <c r="O12" t="n">
-        <v>78174897550</v>
+        <v>79474612700</v>
       </c>
       <c r="P12" t="n">
         <v>139200</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>증시 하락 및 공매도 물량 증가에 따른 부정적 전망. 정부 정책 및 개인 투자자 경험 기반 분석.</t>
+          <t>주가 하락 우려 및 정치 관련 부정적 언급, 공매도 물량 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공매도', '증시 하락', '정부 정책']</t>
+          <t>['주가 하락', '공매도', '정치']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9100</v>
+        <v>9120</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-9.81%</t>
+          <t>'-9.61%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.19</v>
       </c>
       <c r="E13" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F13" t="n">
         <v>69</v>
       </c>
       <c r="G13" t="n">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H13" t="n">
         <v>2.5</v>
@@ -1622,7 +1622,7 @@
         <v>3.69</v>
       </c>
       <c r="O13" t="n">
-        <v>39401961375</v>
+        <v>40003915050</v>
       </c>
       <c r="P13" t="n">
         <v>11690</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>조정 및 횡보 예상, 하한가 및 급락 가능성 언급, 신사업 및 투자 주의 해제 기대감.</t>
+          <t>주가 하락세 지속 및 횡보 예상, 투자주의 종목 관련 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['조정', '하한가', '신사업']</t>
+          <t>['주가 하락', '횡보', '투자주의']</t>
         </is>
       </c>
       <c r="X13" t="n">
